--- a/data/trans_bre/P1803_2016_2023-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1803_2016_2023-Edad-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>-0,6</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>-10,72%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 2,76</t>
+          <t>-4,04; 2,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 4,41</t>
+          <t>-5,36; 4,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-51,08; 76,09</t>
+          <t>-57,22; 71,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-68,78; 167,06</t>
+          <t>-66,2; 163,23</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,01</t>
+          <t>2,29</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 5,27</t>
+          <t>-0,35; 5,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 6,45</t>
+          <t>-1,92; 6,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 169,49</t>
+          <t>-5,92; 159,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,47; 112,7</t>
+          <t>-20,2; 116,6</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-1,97</t>
+          <t>-1,14</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-15,19%</t>
+          <t>-10,25%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 1,22</t>
+          <t>-3,86; 1,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 1,91</t>
+          <t>-4,71; 2,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-55,76; 32,41</t>
+          <t>-54,16; 27,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-37,78; 18,25</t>
+          <t>-36,03; 22,8</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-24,63</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-69,63%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 3,07</t>
+          <t>-2,17; 2,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-58,12; 1,06</t>
+          <t>-2,14; 3,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-34,24; 86,55</t>
+          <t>-35,52; 88,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-86,47; 10,5</t>
+          <t>-17,7; 48,12</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,15</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>73,23%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 5,08</t>
+          <t>-1,63; 4,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,88</t>
+          <t>2,65; 8,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,61; 150,82</t>
+          <t>-30,28; 151,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,06; 121,49</t>
+          <t>26,82; 133,73</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>4,53</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>70,89%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 8,39</t>
+          <t>1,83; 8,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 5,44</t>
+          <t>1,8; 7,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,72; 769,78</t>
+          <t>34,07; 817,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-57,6; 92,04</t>
+          <t>22,71; 159,88</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,35</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>106,53%</t>
+          <t>109,68%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 3,81</t>
+          <t>-1,45; 3,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,56</t>
+          <t>0,86; 5,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-47,49; 254,57</t>
+          <t>-44,28; 246,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,13; 287,05</t>
+          <t>18,75; 313,68</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-5,42</t>
+          <t>1,95</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-36,46%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,94</t>
+          <t>-0,03; 2,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-24,95; 1,69</t>
+          <t>0,52; 3,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 48,36</t>
+          <t>-0,54; 53,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-73,5; 19,99</t>
+          <t>5,72; 45,67</t>
         </is>
       </c>
     </row>
